--- a/tools/1000_websites_sorter/domain_completion_tracker.xlsx
+++ b/tools/1000_websites_sorter/domain_completion_tracker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="video" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="1051">
   <si>
     <t xml:space="preserve">לחיצת קדם</t>
   </si>
@@ -38,6 +38,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans Devanagari"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">לחיצת </t>
     </r>
@@ -1786,60 +1787,36 @@
     <t xml:space="preserve">ffmpeg.org/download.html</t>
   </si>
   <si>
-    <t xml:space="preserve">paceman.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tanksmith.io</t>
-  </si>
-  <si>
     <t xml:space="preserve">raised</t>
   </si>
   <si>
-    <t xml:space="preserve">acolytefight.io  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">app-btn-primary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">antwar.io  </t>
+    <t xml:space="preserve">acolytefight.io</t>
   </si>
   <si>
     <t xml:space="preserve">poki.com/en/g/mouse-mouse-climb-the-house</t>
   </si>
   <si>
-    <t xml:space="preserve">arras.io  </t>
-  </si>
-  <si>
     <t xml:space="preserve">joinButton</t>
   </si>
   <si>
-    <t xml:space="preserve">astroe.io  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">play,nobooster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battleboats.io  </t>
+    <t xml:space="preserve">astroe.io</t>
   </si>
   <si>
     <t xml:space="preserve">CybotCookiebotDialogBodyLevelButtonLevelOptinAllowAll,play_button</t>
   </si>
   <si>
-    <t xml:space="preserve">battledudes.io  </t>
+    <t xml:space="preserve">battledudes.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title-game-playing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brainrotclicker.io/chill-guy-clicker</t>
   </si>
   <si>
     <t xml:space="preserve">playButton</t>
   </si>
   <si>
-    <t xml:space="preserve">bellum.io  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">title-game-playing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brainrotclicker.io/chill-guy-clicker</t>
-  </si>
-  <si>
     <t xml:space="preserve">brutal.io/</t>
   </si>
   <si>
@@ -1855,7 +1832,7 @@
     <t xml:space="preserve">playbtn</t>
   </si>
   <si>
-    <t xml:space="preserve">craftnite.io  </t>
+    <t xml:space="preserve">craftnite.io</t>
   </si>
   <si>
     <t xml:space="preserve">crazysteve.io/</t>
@@ -1864,10 +1841,7 @@
     <t xml:space="preserve">btn-green,btn-green,shipyard-item</t>
   </si>
   <si>
-    <t xml:space="preserve">drednot.io  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoworld.io/</t>
+    <t xml:space="preserve">drednot.io</t>
   </si>
   <si>
     <t xml:space="preserve">game.bitplanets.com/#/game</t>
@@ -1888,12 +1862,6 @@
     <t xml:space="preserve">gulper.io/</t>
   </si>
   <si>
-    <t xml:space="preserve">onetrust-accept-btn-handler,altcha_checkbox,enterGame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moomoo.io/?server=london:PR</t>
-  </si>
-  <si>
     <t xml:space="preserve">css-47sehv</t>
   </si>
   <si>
@@ -1915,16 +1883,10 @@
     <t xml:space="preserve">poki.com/en/g/beauty-salon</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/blocky-blast-puzzle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poki.com/en/g/blumgi-soccer</t>
-  </si>
-  <si>
     <t xml:space="preserve">poki.com/en/g/bounce-ball</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/bulletz-io  </t>
+    <t xml:space="preserve">poki.com/en/g/bulletz-io</t>
   </si>
   <si>
     <t xml:space="preserve">poki.com/en/g/cashchubbies-islands</t>
@@ -1948,24 +1910,15 @@
     <t xml:space="preserve">poki.com/en/g/cube-miner-escape-from-prison</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/digging-master</t>
-  </si>
-  <si>
     <t xml:space="preserve">poki.com/en/g/disaster-arena</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/diva-hair-salon</t>
-  </si>
-  <si>
     <t xml:space="preserve">poki.com/en/g/drive-mad</t>
   </si>
   <si>
     <t xml:space="preserve">poki.com/en/g/dual-cat-max</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/escape-from-school</t>
-  </si>
-  <si>
     <t xml:space="preserve">poki.com/en/g/escape-from-spider</t>
   </si>
   <si>
@@ -2029,7 +1982,7 @@
     <t xml:space="preserve">poki.com/en/g/lurkers-io</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/magicland-io  </t>
+    <t xml:space="preserve">poki.com/en/g/magicland-io</t>
   </si>
   <si>
     <t xml:space="preserve">poki.com/en/g/market-sort</t>
@@ -2098,7 +2051,7 @@
     <t xml:space="preserve">poki.com/en/g/spot-the-differences</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/sprint-league  </t>
+    <t xml:space="preserve">poki.com/en/g/sprint-league</t>
   </si>
   <si>
     <t xml:space="preserve">poki.com/en/g/star-blogger-left-or-right</t>
@@ -2137,7 +2090,7 @@
     <t xml:space="preserve">poki.com/en/g/swole-simulator</t>
   </si>
   <si>
-    <t xml:space="preserve">poki.com/en/g/vectaria-io  </t>
+    <t xml:space="preserve">poki.com/en/g/vectaria-io</t>
   </si>
   <si>
     <t xml:space="preserve">poki.com/en/g/village-craft</t>
@@ -2167,10 +2120,10 @@
     <t xml:space="preserve">button-play</t>
   </si>
   <si>
-    <t xml:space="preserve">skribbl.io  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">slither.io  </t>
+    <t xml:space="preserve">skribbl.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slither.io</t>
   </si>
   <si>
     <t xml:space="preserve">solitaired.com/freecell</t>
@@ -2194,7 +2147,7 @@
     <t xml:space="preserve">voxiom.io/#5Ru1k</t>
   </si>
   <si>
-    <t xml:space="preserve">wings.io  </t>
+    <t xml:space="preserve">wings.io</t>
   </si>
   <si>
     <t xml:space="preserve">www.bubbleshooter.com/</t>
@@ -3303,6 +3256,7 @@
       <color theme="1"/>
       <name val="Noto Sans Devanagari"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -3405,7 +3359,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3433,19 +3387,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBBE33D"/>
-        <bgColor rgb="FF92D050"/>
+        <bgColor rgb="FFC3D69B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FF9C0006"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFBBE33D"/>
       </patternFill>
     </fill>
     <fill>
@@ -3518,16 +3466,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3535,15 +3487,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3559,7 +3511,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3599,15 +3551,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3615,19 +3567,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3639,23 +3591,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3663,27 +3615,31 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3691,15 +3647,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3759,8 +3711,8 @@
       <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FFBBE33D"/>
+      <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
@@ -3961,625 +3913,625 @@
   <dimension ref="A1:C114"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2"/>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2"/>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2"/>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="3"/>
+      <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5"/>
-      <c r="C18" s="3" t="s">
+      <c r="A18" s="6"/>
+      <c r="C18" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4"/>
-      <c r="C29" s="3" t="s">
+      <c r="A29" s="5"/>
+      <c r="C29" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
-      <c r="B30" s="0" t="s">
+      <c r="A30" s="5"/>
+      <c r="B30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4"/>
-      <c r="C31" s="3" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="6"/>
-      <c r="C33" s="3" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="9" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="4"/>
-      <c r="C72" s="8" t="s">
+      <c r="B72" s="5"/>
+      <c r="C72" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="9" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="9" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="4"/>
-      <c r="C82" s="8" t="s">
+      <c r="B82" s="5"/>
+      <c r="C82" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="9" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="9" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="9" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="9"/>
+      <c r="C95" s="10"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="10"/>
+      <c r="C96" s="11"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="9"/>
+      <c r="C97" s="10"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="4"/>
-      <c r="C98" s="9"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="10"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="9"/>
+      <c r="C99" s="10"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="10"/>
+      <c r="C100" s="11"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="9"/>
+      <c r="C101" s="10"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="6"/>
-      <c r="C102" s="9"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="10"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C103" s="10"/>
+      <c r="C103" s="11"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C104" s="10"/>
+      <c r="C104" s="11"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="9"/>
+      <c r="C105" s="10"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C106" s="10"/>
+      <c r="C106" s="11"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C107" s="10"/>
+      <c r="C107" s="11"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C108" s="9"/>
+      <c r="C108" s="10"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C109" s="10"/>
+      <c r="C109" s="11"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C110" s="10"/>
+      <c r="C110" s="11"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C111" s="10"/>
+      <c r="C111" s="11"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C112" s="10"/>
+      <c r="C112" s="11"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C113" s="10"/>
+      <c r="C113" s="11"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="6"/>
-      <c r="C114" s="9"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4656,664 +4608,664 @@
   <dimension ref="A1:C126"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4"/>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="9" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
-      <c r="C8" s="8"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="9" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="9" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4"/>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="9" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="9" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="9" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="9" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4"/>
-      <c r="C31" s="8" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="9" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="9" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="9" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="9" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4"/>
-      <c r="C37" s="8" t="s">
+      <c r="B37" s="5"/>
+      <c r="C37" s="9" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="9" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4"/>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="5"/>
+      <c r="C40" s="9" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="9" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="9" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="9" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="9" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="9" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4"/>
-      <c r="C46" s="8" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="9" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="9" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="9" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="9" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="9" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="9" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="9" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="4"/>
-      <c r="C54" s="8" t="s">
+      <c r="B54" s="5"/>
+      <c r="C54" s="9" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="9" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="4"/>
-      <c r="C56" s="8" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="9" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="9" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="9" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="9" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="9" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="9" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="9" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="9" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="9" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="9" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="9" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="6"/>
-      <c r="C69" s="8" t="s">
+      <c r="B69" s="7"/>
+      <c r="C69" s="9" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="9" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="9" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="9" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="9" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="9" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="6"/>
-      <c r="C76" s="8" t="s">
+      <c r="B76" s="7"/>
+      <c r="C76" s="9" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="9" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="9" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="6"/>
+      <c r="B79" s="7"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="4"/>
-      <c r="C81" s="9"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="10"/>
+      <c r="C82" s="11"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="4"/>
-      <c r="C83" s="10"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="11"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="9"/>
+      <c r="C84" s="10"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="4"/>
-      <c r="C85" s="10"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="11"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="4"/>
-      <c r="C86" s="9"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="4"/>
-      <c r="C87" s="9"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="10"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="10"/>
+      <c r="C88" s="11"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="10"/>
+      <c r="C89" s="11"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="4"/>
-      <c r="C90" s="9"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="10"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="4"/>
-      <c r="C91" s="9"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="10"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C92" s="10"/>
+      <c r="C92" s="11"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="6"/>
-      <c r="C93" s="9"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="10"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="10"/>
+      <c r="C94" s="11"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="6"/>
+      <c r="B102" s="7"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="6"/>
+      <c r="B103" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="6"/>
+      <c r="B106" s="7"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="6"/>
+      <c r="B108" s="7"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="6"/>
+      <c r="B110" s="7"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="6"/>
+      <c r="B111" s="7"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="6"/>
+      <c r="B114" s="7"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="6"/>
+      <c r="B119" s="7"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="6"/>
+      <c r="B120" s="7"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="6"/>
+      <c r="B126" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5369,855 +5321,855 @@
   <dimension ref="A1:C222"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="13" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="13" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="13" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="13" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="13" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="13" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="13" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="13" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="13" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="13" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="13" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="13" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="13" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="13" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="13" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="13" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="13" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="13" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="13" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="13" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="13" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="13" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="13" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="13" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="13" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="13" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="13" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="13" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="13" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="13" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="13" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="13" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="13" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="13" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="13" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="13" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="13" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="13" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="13" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="13" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C111" s="13"/>
+      <c r="C111" s="14"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C112" s="13"/>
+      <c r="C112" s="14"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C113" s="13"/>
+      <c r="C113" s="14"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C114" s="13"/>
+      <c r="C114" s="14"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C115" s="13"/>
+      <c r="C115" s="14"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C116" s="13"/>
+      <c r="C116" s="14"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C117" s="13"/>
+      <c r="C117" s="14"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C118" s="13"/>
+      <c r="C118" s="14"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C119" s="13"/>
+      <c r="C119" s="14"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C120" s="13"/>
+      <c r="C120" s="14"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C121" s="13"/>
+      <c r="C121" s="14"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C122" s="13"/>
+      <c r="C122" s="14"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C123" s="13"/>
+      <c r="C123" s="14"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C124" s="13"/>
+      <c r="C124" s="14"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C125" s="13"/>
+      <c r="C125" s="14"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C126" s="13"/>
+      <c r="C126" s="14"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C127" s="13"/>
+      <c r="C127" s="14"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C128" s="13"/>
+      <c r="C128" s="14"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C129" s="13"/>
+      <c r="C129" s="14"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C130" s="13"/>
+      <c r="C130" s="14"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C131" s="13"/>
+      <c r="C131" s="14"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C132" s="13"/>
+      <c r="C132" s="14"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C133" s="13"/>
+      <c r="C133" s="14"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C134" s="13"/>
+      <c r="C134" s="14"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C135" s="13"/>
+      <c r="C135" s="14"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C136" s="13"/>
+      <c r="C136" s="14"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C137" s="13"/>
+      <c r="C137" s="14"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C138" s="13"/>
+      <c r="C138" s="14"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C139" s="13"/>
+      <c r="C139" s="14"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C140" s="13"/>
+      <c r="C140" s="14"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C141" s="13"/>
+      <c r="C141" s="14"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C142" s="13"/>
+      <c r="C142" s="14"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C143" s="13"/>
+      <c r="C143" s="14"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C144" s="13"/>
+      <c r="C144" s="14"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C145" s="13"/>
+      <c r="C145" s="14"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C146" s="13"/>
+      <c r="C146" s="14"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C147" s="13"/>
+      <c r="C147" s="14"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C148" s="13"/>
+      <c r="C148" s="14"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C149" s="13"/>
+      <c r="C149" s="14"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C150" s="13"/>
+      <c r="C150" s="14"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C151" s="13"/>
+      <c r="C151" s="14"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C152" s="13"/>
+      <c r="C152" s="14"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C153" s="13"/>
+      <c r="C153" s="14"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C154" s="13"/>
+      <c r="C154" s="14"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C155" s="13"/>
+      <c r="C155" s="14"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C156" s="13"/>
+      <c r="C156" s="14"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C157" s="13"/>
+      <c r="C157" s="14"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C158" s="13"/>
+      <c r="C158" s="14"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C159" s="13"/>
+      <c r="C159" s="14"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C160" s="13"/>
+      <c r="C160" s="14"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C161" s="13"/>
+      <c r="C161" s="14"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C162" s="13"/>
+      <c r="C162" s="14"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C163" s="13"/>
+      <c r="C163" s="14"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C164" s="13"/>
+      <c r="C164" s="14"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C165" s="13"/>
+      <c r="C165" s="14"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C166" s="13"/>
+      <c r="C166" s="14"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C167" s="13"/>
+      <c r="C167" s="14"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C168" s="13"/>
+      <c r="C168" s="14"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C169" s="13"/>
+      <c r="C169" s="14"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C170" s="13"/>
+      <c r="C170" s="14"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C171" s="13"/>
+      <c r="C171" s="14"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C172" s="13"/>
+      <c r="C172" s="14"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C173" s="13"/>
+      <c r="C173" s="14"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C174" s="13"/>
+      <c r="C174" s="14"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C175" s="13"/>
+      <c r="C175" s="14"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C176" s="13"/>
+      <c r="C176" s="14"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C177" s="13"/>
+      <c r="C177" s="14"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C178" s="13"/>
+      <c r="C178" s="14"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C179" s="13"/>
+      <c r="C179" s="14"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C180" s="13"/>
+      <c r="C180" s="14"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C181" s="13"/>
+      <c r="C181" s="14"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C182" s="13"/>
+      <c r="C182" s="14"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C183" s="13"/>
+      <c r="C183" s="14"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C184" s="13"/>
+      <c r="C184" s="14"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C185" s="13"/>
+      <c r="C185" s="14"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C186" s="13"/>
+      <c r="C186" s="14"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C187" s="13"/>
+      <c r="C187" s="14"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C188" s="13"/>
+      <c r="C188" s="14"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C189" s="13"/>
+      <c r="C189" s="14"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C190" s="13"/>
+      <c r="C190" s="14"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C191" s="13"/>
+      <c r="C191" s="14"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C192" s="13"/>
+      <c r="C192" s="14"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C193" s="13"/>
+      <c r="C193" s="14"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C194" s="13"/>
+      <c r="C194" s="14"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C195" s="13"/>
+      <c r="C195" s="14"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C196" s="13"/>
+      <c r="C196" s="14"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C197" s="13"/>
+      <c r="C197" s="14"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C198" s="13"/>
+      <c r="C198" s="14"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C199" s="13"/>
+      <c r="C199" s="14"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C200" s="13"/>
+      <c r="C200" s="14"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C201" s="13"/>
+      <c r="C201" s="14"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C202" s="13"/>
+      <c r="C202" s="14"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C203" s="13"/>
+      <c r="C203" s="14"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C204" s="10"/>
+      <c r="C204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C205" s="10"/>
+      <c r="C205" s="11"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C206" s="10"/>
+      <c r="C206" s="11"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C207" s="10"/>
+      <c r="C207" s="11"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C208" s="10"/>
+      <c r="C208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C209" s="10"/>
+      <c r="C209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C210" s="10"/>
+      <c r="C210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C211" s="10"/>
+      <c r="C211" s="11"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C212" s="10"/>
+      <c r="C212" s="11"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C213" s="10"/>
+      <c r="C213" s="11"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C214" s="10"/>
+      <c r="C214" s="11"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C215" s="10"/>
+      <c r="C215" s="11"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C216" s="10"/>
+      <c r="C216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C217" s="10"/>
+      <c r="C217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C218" s="10"/>
+      <c r="C218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C219" s="10"/>
+      <c r="C219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C220" s="10"/>
+      <c r="C220" s="11"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C221" s="10"/>
+      <c r="C221" s="11"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C222" s="10"/>
+      <c r="C222" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6314,781 +6266,781 @@
   <dimension ref="A1:D141"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="72.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="72.97"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="4"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="15" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4"/>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="15" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5"/>
-      <c r="C5" s="14" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="15" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="15" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5"/>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="15" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="15" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5"/>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="15" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5"/>
-      <c r="C11" s="14" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="15" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="15" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5"/>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="15" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5"/>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="15" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="15" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5"/>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="15" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5"/>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="15" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5"/>
-      <c r="C19" s="14" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="15" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5"/>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="D20" s="15"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5"/>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="D21" s="16"/>
+      <c r="D21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5"/>
-      <c r="C22" s="14" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="D22" s="15"/>
+      <c r="D22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="D23" s="16"/>
+      <c r="D23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5"/>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="D24" s="15"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5"/>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="D25" s="16"/>
+      <c r="D25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="D26" s="17"/>
+      <c r="D26" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="14" t="s">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="D27" s="17"/>
+      <c r="D27" s="18"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="14" t="s">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="D28" s="18"/>
+      <c r="D28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="14" t="s">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="D29" s="18"/>
+      <c r="D29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="D30" s="18"/>
+      <c r="D30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="14" t="s">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="D31" s="18"/>
+      <c r="D31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="D32" s="18"/>
+      <c r="D32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="14" t="s">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="D33" s="18"/>
+      <c r="D33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="D34" s="18"/>
+      <c r="D34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="14" t="s">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="D35" s="18"/>
+      <c r="D35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="D36" s="18"/>
+      <c r="D36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="15" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="14" t="s">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="15" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="14" t="s">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="15" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="19" t="s">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="20" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="19" t="s">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="20" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="19" t="s">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="20" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="19" t="s">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="20" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="5"/>
-      <c r="C44" s="19" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="20" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="20"/>
-      <c r="C45" s="19" t="s">
+      <c r="B45" s="21"/>
+      <c r="C45" s="20" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="5"/>
-      <c r="C46" s="19" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="20" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="5"/>
-      <c r="C47" s="19" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="20" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="5"/>
-      <c r="C48" s="19" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="20" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="5"/>
-      <c r="C49" s="19" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="20" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5"/>
-      <c r="C50" s="19" t="s">
+      <c r="A50" s="6"/>
+      <c r="C50" s="20" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="19" t="s">
+      <c r="A51" s="22"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="20" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="5"/>
-      <c r="C52" s="19" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="20" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="19" t="s">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="20" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="19" t="s">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="20" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="19" t="s">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="20" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="19" t="s">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="20" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="19" t="s">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="20" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="19" t="s">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="20" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="19" t="s">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="20" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="19" t="s">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="20" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="19" t="s">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="20" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="19" t="s">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="20" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="19" t="s">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="20" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="19" t="s">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="20" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="19" t="s">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="20" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="19" t="s">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="20" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="19" t="s">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="20" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="19" t="s">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="20" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="19" t="s">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="20" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="19" t="s">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="20" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="19" t="s">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="20" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="19" t="s">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="20" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="19" t="s">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="20" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="19" t="s">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="20" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="19" t="s">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="20" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="19" t="s">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="20" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="19" t="s">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="20" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="19" t="s">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="20" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="19" t="s">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="20" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="19" t="s">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="20" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="19" t="s">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="20" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="19" t="s">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="20" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="19" t="s">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="20" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="5"/>
-      <c r="C84" s="19" t="s">
+      <c r="B84" s="6"/>
+      <c r="C84" s="20" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="19" t="s">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="20" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="19" t="s">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="20" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="19" t="s">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="20" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5"/>
-      <c r="C88" s="19" t="s">
+      <c r="A88" s="6"/>
+      <c r="C88" s="20" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="19" t="s">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="20" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="19" t="s">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="20" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="19" t="s">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="20" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="19" t="s">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="20" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="19" t="s">
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="20" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="19" t="s">
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="20" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="5"/>
-      <c r="C95" s="19" t="s">
+      <c r="A95" s="6"/>
+      <c r="C95" s="20" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="19" t="s">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="20" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="5"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="15"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="16"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="5"/>
-      <c r="B98" s="5"/>
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="5"/>
-      <c r="B101" s="5"/>
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="5"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="15"/>
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="16"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="5"/>
+      <c r="B103" s="6"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="5"/>
+      <c r="B104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="22"/>
+      <c r="B105" s="23"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C106" s="15"/>
+      <c r="C106" s="16"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="5"/>
+      <c r="B107" s="6"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="5"/>
+      <c r="B108" s="6"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="5"/>
+      <c r="B109" s="6"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="5"/>
-      <c r="B110" s="5"/>
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="5"/>
+      <c r="B111" s="6"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="5"/>
+      <c r="B112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="5"/>
+      <c r="B113" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="5"/>
+      <c r="B115" s="6"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="5"/>
+      <c r="B116" s="6"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="5"/>
+      <c r="B117" s="6"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="5"/>
+      <c r="B118" s="6"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="5"/>
+      <c r="B119" s="6"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="5"/>
+      <c r="B120" s="6"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="5"/>
+      <c r="B121" s="6"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="5"/>
+      <c r="B122" s="6"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="5"/>
+      <c r="B123" s="6"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="5"/>
+      <c r="B124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="5"/>
+      <c r="B125" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C127" s="19"/>
+      <c r="C127" s="20"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C131" s="23"/>
+      <c r="C131" s="24"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C132" s="23"/>
+      <c r="C132" s="24"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C135" s="23"/>
+      <c r="C135" s="24"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C137" s="23"/>
+      <c r="C137" s="24"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C138" s="23"/>
+      <c r="C138" s="24"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C139" s="23"/>
+      <c r="C139" s="24"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C141" s="23"/>
+      <c r="C141" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7128,758 +7080,758 @@
   <dimension ref="A1:G126"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="24" width="74.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="74.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="28" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="29" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="28" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5"/>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="28" t="s">
         <v>447</v>
       </c>
-      <c r="F8" s="33"/>
+      <c r="F8" s="34"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="28" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="20" t="s">
         <v>451</v>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="35" t="s">
         <v>452</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="28" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="35" t="s">
         <v>454</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="30" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="36" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="36" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="36" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="28" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5"/>
-      <c r="C17" s="29" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="30" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="28" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="37" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5"/>
-      <c r="C20" s="36" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="37" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="30" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="28" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5"/>
-      <c r="C24" s="37" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="38" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="30" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="34"/>
-      <c r="C26" s="35" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5"/>
-      <c r="C27" s="37" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="38" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5"/>
-      <c r="C28" s="37" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="38" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="28" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="38" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="28" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5"/>
-      <c r="C32" s="37" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="38" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="30" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="28" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="30" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="C36" s="28" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="30" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="36" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="35" t="s">
         <v>498</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="28" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="5"/>
-      <c r="C41" s="29" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="30" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="35" t="s">
         <v>503</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="28" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="28" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="C44" s="27" t="s">
+      <c r="C44" s="28" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="28" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="28" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="5"/>
-      <c r="C47" s="37" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="38" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="35" t="s">
         <v>513</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="30" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="34" t="s">
+      <c r="B49" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="28" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="34"/>
-      <c r="C50" s="37" t="s">
+      <c r="B50" s="35"/>
+      <c r="C50" s="38" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="34" t="s">
+      <c r="B51" s="35" t="s">
         <v>518</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="C51" s="28" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="35" t="s">
         <v>520</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="C52" s="28" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="28" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="28" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C55" s="27" t="s">
+      <c r="C55" s="28" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="C56" s="27" t="s">
+      <c r="C56" s="28" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="28" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="C58" s="28" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="C59" s="28" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="C60" s="27" t="s">
+      <c r="C60" s="28" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C61" s="28" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="C62" s="27" t="s">
+      <c r="C62" s="28" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="28" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="C64" s="32" t="s">
+      <c r="C64" s="33" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="32" t="s">
+      <c r="C65" s="33" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="C66" s="32" t="s">
+      <c r="C66" s="33" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="C67" s="32" t="s">
+      <c r="C67" s="33" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="C68" s="32" t="s">
+      <c r="C68" s="33" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="30" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="C70" s="35" t="s">
+      <c r="C70" s="36" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="27" t="s">
+      <c r="C71" s="28" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="5"/>
-      <c r="C72" s="27" t="s">
+      <c r="B72" s="6"/>
+      <c r="C72" s="28" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="29" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="C74" s="32" t="s">
+      <c r="C74" s="33" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="4"/>
-      <c r="C75" s="32" t="s">
+      <c r="B75" s="5"/>
+      <c r="C75" s="33" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="C76" s="32" t="s">
+      <c r="C76" s="33" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="C77" s="32" t="s">
+      <c r="C77" s="33" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="28" t="s">
+      <c r="C78" s="29" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="28" t="s">
+      <c r="C79" s="29" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="C80" s="32" t="s">
+      <c r="C80" s="33" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C81" s="32" t="s">
+      <c r="C81" s="33" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="C82" s="32" t="s">
+      <c r="C82" s="33" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="C83" s="32" t="s">
+      <c r="C83" s="33" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="28"/>
+      <c r="C84" s="29"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="0"/>
+      <c r="C85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="0"/>
+      <c r="C86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="0"/>
+      <c r="C87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="0"/>
+      <c r="C88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="32"/>
+      <c r="C89" s="33"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="0"/>
+      <c r="C90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="38"/>
+      <c r="C91" s="39"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="6"/>
-      <c r="C92" s="28"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="29"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C93" s="32"/>
+      <c r="C93" s="33"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="38"/>
+      <c r="C94" s="39"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="0"/>
+      <c r="C95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="0"/>
+      <c r="C96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="0"/>
+      <c r="C97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C98" s="0"/>
+      <c r="C98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="0"/>
+      <c r="C99" s="1"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="0"/>
+      <c r="C100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="0"/>
+      <c r="C101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C102" s="0"/>
+      <c r="C102" s="1"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C103" s="0"/>
+      <c r="C103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C104" s="0"/>
+      <c r="C104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="0"/>
+      <c r="C105" s="1"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C106" s="0"/>
+      <c r="C106" s="1"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C107" s="0"/>
+      <c r="C107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C108" s="0"/>
+      <c r="C108" s="1"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C109" s="0"/>
+      <c r="C109" s="1"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C110" s="0"/>
+      <c r="C110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C111" s="0"/>
+      <c r="C111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C112" s="0"/>
+      <c r="C112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C113" s="0"/>
+      <c r="C113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C114" s="0"/>
+      <c r="C114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C115" s="0"/>
+      <c r="C115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C116" s="0"/>
+      <c r="C116" s="1"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C117" s="0"/>
+      <c r="C117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C118" s="0"/>
+      <c r="C118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C119" s="0"/>
+      <c r="C119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C120" s="0"/>
+      <c r="C120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C121" s="0"/>
+      <c r="C121" s="1"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C122" s="0"/>
+      <c r="C122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C123" s="0"/>
+      <c r="C123" s="1"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C124" s="0"/>
+      <c r="C124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C125" s="0"/>
+      <c r="C125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C126" s="0"/>
+      <c r="C126" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7900,756 +7852,713 @@
   <dimension ref="A1:C128"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="40"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="40"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="40"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="40" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="40"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="40"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="40"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="40" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="C17" s="40" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="40"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="40" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>575</v>
-      </c>
-      <c r="C4" s="39" t="s">
+      <c r="C21" s="40" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="7"/>
+      <c r="C24" s="40"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="33" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="29" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="40" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="33" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="29"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="40"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="29" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="40" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="40" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="29" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="29" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C38" s="29" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C39" s="29" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="33" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="33" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C42" s="33"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="29" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C44" s="33"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C45" s="29" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C46" s="33" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C47" s="40"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C48" s="40" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C49" s="33" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C50" s="33" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C51" s="29" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C52" s="29" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C53" s="29" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C54" s="33" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C55" s="29" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C56" s="41" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C57" s="41" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C58" s="41" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C59" s="42" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="42" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C61" s="43" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C62" s="43" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C63" s="43" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="41" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C65" s="42" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C66" s="43" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C67" s="41" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C68" s="41" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C69" s="41" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C70" s="41" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C71" s="41" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="43" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C73" s="43" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C74" s="41" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="43" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C76" s="41" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C77" s="41" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="41" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="43" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C80" s="43" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C81" s="41" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="43" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C83" s="43" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C84" s="41" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C85" s="43" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C86" s="41" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="41" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C88" s="42" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C89" s="41" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C90" s="42" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C91" s="43" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C92" s="41" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C93" s="42" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C94" s="43" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C95" s="41" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C96" s="41" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C97" s="43" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="42" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C99" s="42" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="43" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C101" s="42" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C102" s="42" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C103" s="43" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C104" s="43" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="41" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="43" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C107" s="41" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="42" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="43" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="41" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="42" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C112" s="42" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C113" s="41" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C114" s="41" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="41" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C116" s="41" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="1" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>577</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="39" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="39" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>581</v>
-      </c>
-      <c r="C8" s="39" t="s">
+      <c r="C117" s="41" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C118" s="41" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C119" s="41" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="41" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="1" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>585</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>587</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>589</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>587</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>592</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="39" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
-        <v>595</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
-        <v>598</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="39" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="39" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
-        <v>603</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
-        <v>605</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
-        <v>609</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="41" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="42" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="39" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="41" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="42" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="39" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="42" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="39" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="39" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="42" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="42" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="42" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="42" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="41" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="41" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="41" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="42" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="41" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="42" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="41" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="39" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="39" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="41" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="41" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="42" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="42" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="42" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="41" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="42" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="39" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="39" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C58" s="39" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="41" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="41" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="42" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="42" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="42" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="39" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="41" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="42" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="39" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="39" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="39" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C70" s="39" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="39" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="42" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C73" s="42" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="39" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C75" s="42" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C76" s="39" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="39" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="39" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="42" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C80" s="42" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C81" s="39" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="42" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C83" s="42" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="39" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="42" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="39" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="39" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="41" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="39" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="41" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="42" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C92" s="39" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C93" s="41" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="42" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="39" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="39" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="42" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C98" s="41" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="41" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="42" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="41" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C102" s="41" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C103" s="42" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C104" s="42" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="39" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C106" s="42" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C107" s="39" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C108" s="41" t="s">
+      <c r="C121" s="41" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C109" s="42" t="s">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C122" s="41" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C110" s="39" t="s">
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="41" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C111" s="41" t="s">
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C124" s="41" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C112" s="41" t="s">
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="1" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="C113" s="39" t="s">
+      <c r="C125" s="41" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="0" t="s">
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C114" s="39" t="s">
+      <c r="C126" s="41" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C115" s="39" t="s">
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C127" s="41" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C116" s="39" t="s">
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="0" t="s">
-        <v>581</v>
-      </c>
-      <c r="C117" s="39" t="s">
+      <c r="C128" s="41" t="s">
         <v>703</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B118" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="C118" s="39" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="C119" s="39" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C120" s="39" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="0" t="s">
-        <v>587</v>
-      </c>
-      <c r="C121" s="39" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C122" s="39" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C123" s="39" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C124" s="39" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="0" t="s">
-        <v>713</v>
-      </c>
-      <c r="C125" s="39" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="C126" s="39" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="n">
-        <v>90</v>
-      </c>
-      <c r="B127" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="C127" s="39" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="B128" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="C128" s="39" t="s">
-        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -8671,932 +8580,932 @@
   <dimension ref="A1:C126"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="35" t="s">
+        <v>704</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="35"/>
+      <c r="C3" s="44" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="45" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="44" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="45" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>720</v>
       </c>
-      <c r="C2" s="43" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="34"/>
-      <c r="C3" s="43" t="s">
+      <c r="C13" s="44" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="44" t="s">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="C14" s="44" t="s">
         <v>724</v>
       </c>
-      <c r="C5" s="44" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="43" t="s">
+      <c r="C15" s="44" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="44" t="s">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="44" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C8" s="43" t="s">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="C17" s="45" t="s">
         <v>729</v>
       </c>
-      <c r="C9" s="43" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="35" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="C18" s="45" t="s">
         <v>731</v>
       </c>
-      <c r="C10" s="43" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="C19" s="45" t="s">
         <v>733</v>
       </c>
-      <c r="C11" s="44" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="1" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C21" s="44" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="6" t="s">
         <v>737</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C22" s="45" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="24" t="s">
         <v>739</v>
       </c>
-      <c r="C14" s="43" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="C24" s="45" t="s">
         <v>741</v>
       </c>
-      <c r="C15" s="43" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="6" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="43" t="s">
+      <c r="C25" s="45" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C26" s="45" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="34" t="s">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C27" s="44" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
         <v>748</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C28" s="45" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="0" t="s">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="45" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C21" s="43" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="6" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
+      <c r="C31" s="45" t="s">
         <v>753</v>
       </c>
-      <c r="C22" s="44" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="6"/>
+      <c r="C32" s="44" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="23" t="s">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="44" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="35"/>
+      <c r="C34" s="24" t="s">
         <v>756</v>
       </c>
-      <c r="C24" s="44" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="6" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
+      <c r="C35" s="44" t="s">
         <v>758</v>
       </c>
-      <c r="C25" s="44" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="44" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="35" t="s">
         <v>760</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C37" s="44" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="35" t="s">
         <v>762</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C38" s="44" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C39" s="44" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="44" t="s">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="35" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="0" t="s">
+      <c r="C40" s="44" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5" t="s">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="C41" s="45" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5"/>
-      <c r="C32" s="43" t="s">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C42" s="45" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="43" t="s">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="6" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="34"/>
-      <c r="C34" s="23" t="s">
+      <c r="C43" s="45" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="s">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C44" s="45" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="43" t="s">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="34" t="s">
+      <c r="C45" s="45" t="s">
         <v>776</v>
       </c>
-      <c r="C37" s="43" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="6" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="34" t="s">
+      <c r="C46" s="45" t="s">
         <v>778</v>
       </c>
-      <c r="C38" s="43" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="6" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="s">
+      <c r="C47" s="45" t="s">
         <v>780</v>
       </c>
-      <c r="C39" s="43" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="6" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="34" t="s">
+      <c r="C48" s="45" t="s">
         <v>782</v>
       </c>
-      <c r="C40" s="43" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="6" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="5" t="s">
+      <c r="C49" s="45" t="s">
         <v>784</v>
       </c>
-      <c r="C41" s="44" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="6" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="44" t="s">
+      <c r="C50" s="44" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="5" t="s">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="6" t="s">
         <v>787</v>
       </c>
-      <c r="C43" s="44" t="s">
+      <c r="C51" s="45" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="5" t="s">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="C44" s="44" t="s">
+      <c r="C52" s="45" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="5" t="s">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="6" t="s">
         <v>791</v>
       </c>
-      <c r="C45" s="44" t="s">
+      <c r="C53" s="45" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="5" t="s">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="6" t="s">
         <v>793</v>
       </c>
-      <c r="C46" s="44" t="s">
+      <c r="C54" s="45" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="5" t="s">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C55" s="45" t="s">
         <v>795</v>
       </c>
-      <c r="C47" s="44" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="35" t="s">
+        <v>781</v>
+      </c>
+      <c r="C56" s="44" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="5" t="s">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C57" s="45" t="s">
         <v>797</v>
       </c>
-      <c r="C48" s="44" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="C58" s="45" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="5" t="s">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C59" s="45" t="s">
         <v>799</v>
       </c>
-      <c r="C49" s="44" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="45" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="5" t="s">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C61" s="45" t="s">
         <v>801</v>
       </c>
-      <c r="C50" s="43" t="s">
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C62" s="45" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="5" t="s">
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C63" s="45" t="s">
         <v>803</v>
       </c>
-      <c r="C51" s="44" t="s">
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="44" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="5" t="s">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C65" s="45" t="s">
         <v>805</v>
       </c>
-      <c r="C52" s="44" t="s">
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="6"/>
+      <c r="C66" s="45" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="5" t="s">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="35" t="s">
         <v>807</v>
       </c>
-      <c r="C53" s="44" t="s">
+      <c r="C67" s="44" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="5" t="s">
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="6" t="s">
         <v>809</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="C68" s="45" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="44" t="s">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="6" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="34" t="s">
-        <v>797</v>
-      </c>
-      <c r="C56" s="43" t="s">
+      <c r="C69" s="45" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="44" t="s">
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="6" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="C58" s="44" t="s">
+      <c r="C70" s="45" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="44" t="s">
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="6" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="44" t="s">
+      <c r="C71" s="45" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="44" t="s">
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="6" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="44" t="s">
+      <c r="C72" s="45" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="44" t="s">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="1" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="43" t="s">
+      <c r="C73" s="44" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="44" t="s">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C74" s="45" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="5"/>
-      <c r="C66" s="44" t="s">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="6" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="34" t="s">
+      <c r="C75" s="44" t="s">
         <v>823</v>
       </c>
-      <c r="C67" s="43" t="s">
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C76" s="44" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="5" t="s">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="6" t="s">
         <v>825</v>
       </c>
-      <c r="C68" s="44" t="s">
+      <c r="C77" s="44" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="5" t="s">
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="6" t="s">
         <v>827</v>
       </c>
-      <c r="C69" s="44" t="s">
+      <c r="C78" s="45" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="5" t="s">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="6" t="s">
         <v>829</v>
       </c>
-      <c r="C70" s="44" t="s">
+      <c r="C79" s="45" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="5" t="s">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="C71" s="44" t="s">
+      <c r="C80" s="45" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="5" t="s">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="6" t="s">
         <v>833</v>
       </c>
-      <c r="C72" s="44" t="s">
+      <c r="C81" s="45" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="0" t="s">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C82" s="44" t="s">
         <v>835</v>
       </c>
-      <c r="C73" s="43" t="s">
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="6" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="44" t="s">
+      <c r="C83" s="45" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="5" t="s">
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="C75" s="43" t="s">
+      <c r="C84" s="45" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="C76" s="43" t="s">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="6" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="5" t="s">
+      <c r="C85" s="45" t="s">
         <v>841</v>
       </c>
-      <c r="C77" s="43" t="s">
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="6" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="5" t="s">
+      <c r="C86" s="45" t="s">
         <v>843</v>
       </c>
-      <c r="C78" s="44" t="s">
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C87" s="45" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="5" t="s">
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C88" s="45" t="s">
         <v>845</v>
       </c>
-      <c r="C79" s="44" t="s">
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="6" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="5" t="s">
+      <c r="C89" s="45" t="s">
         <v>847</v>
       </c>
-      <c r="C80" s="44" t="s">
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="6" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="5" t="s">
+      <c r="C90" s="45" t="s">
         <v>849</v>
       </c>
-      <c r="C81" s="44" t="s">
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C91" s="45" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="C82" s="43" t="s">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="6" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="5" t="s">
+      <c r="C92" s="45" t="s">
         <v>852</v>
       </c>
-      <c r="C83" s="44" t="s">
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="6" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="5" t="s">
+      <c r="C93" s="45" t="s">
         <v>854</v>
       </c>
-      <c r="C84" s="44" t="s">
+    </row>
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="6" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="5" t="s">
+      <c r="C94" s="44" t="s">
         <v>856</v>
       </c>
-      <c r="C85" s="44" t="s">
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="1" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="5" t="s">
+      <c r="C95" s="45" t="s">
         <v>858</v>
       </c>
-      <c r="C86" s="44" t="s">
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="6" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="C87" s="44" t="s">
+      <c r="C96" s="45" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="44" t="s">
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="6" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="5" t="s">
+      <c r="C97" s="45" t="s">
         <v>862</v>
       </c>
-      <c r="C89" s="44" t="s">
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="45" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="5" t="s">
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="6"/>
+      <c r="C99" s="24" t="s">
         <v>864</v>
       </c>
-      <c r="C90" s="44" t="s">
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="1" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="44" t="s">
+      <c r="C100" s="45" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="5" t="s">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C101" s="45" t="s">
         <v>867</v>
       </c>
-      <c r="C92" s="44" t="s">
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="6" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="5" t="s">
+      <c r="C102" s="45" t="s">
         <v>869</v>
       </c>
-      <c r="C93" s="44" t="s">
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="6" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="5" t="s">
+      <c r="C103" s="45" t="s">
         <v>871</v>
       </c>
-      <c r="C94" s="43" t="s">
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="6" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="0" t="s">
+      <c r="C104" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C95" s="44" t="s">
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C105" s="45" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="5" t="s">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="C96" s="44" t="s">
+      <c r="C106" s="44" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="5" t="s">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C107" s="44" t="s">
         <v>877</v>
       </c>
-      <c r="C97" s="44" t="s">
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="6" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C98" s="44" t="s">
+      <c r="C108" s="45" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="5"/>
-      <c r="C99" s="23" t="s">
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="0" t="s">
+      <c r="B109" s="6" t="s">
         <v>881</v>
       </c>
-      <c r="C100" s="44" t="s">
+      <c r="C109" s="45" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="44" t="s">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="7" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="5" t="s">
+      <c r="C110" s="44" t="s">
         <v>884</v>
       </c>
-      <c r="C102" s="44" t="s">
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="C111" s="45" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="5" t="s">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="C103" s="44" t="s">
+      <c r="C112" s="45" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="5" t="s">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="C104" s="0" t="s">
+      <c r="C113" s="44" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="0" t="s">
-        <v>724</v>
-      </c>
-      <c r="C105" s="44" t="s">
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="7" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="5" t="s">
+      <c r="C114" s="44" t="s">
         <v>891</v>
       </c>
-      <c r="C106" s="43" t="s">
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="7" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="0" t="s">
-        <v>609</v>
-      </c>
-      <c r="C107" s="43" t="s">
+      <c r="C115" s="44" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="5" t="s">
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="7" t="s">
         <v>894</v>
       </c>
-      <c r="C108" s="44" t="s">
+      <c r="C116" s="44" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="C117" s="44" t="s">
         <v>897</v>
       </c>
-      <c r="C109" s="44" t="s">
+    </row>
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="C118" s="44" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="7" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="6" t="s">
+      <c r="C119" s="44" t="s">
         <v>899</v>
       </c>
-      <c r="C110" s="43" t="s">
+    </row>
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="C120" s="44" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="C111" s="44" t="s">
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="5" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="4" t="s">
+      <c r="C121" s="45" t="s">
         <v>902</v>
       </c>
-      <c r="C112" s="44" t="s">
+    </row>
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="7" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="4" t="s">
+      <c r="C122" s="45" t="s">
         <v>904</v>
       </c>
-      <c r="C113" s="43" t="s">
+    </row>
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="44" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="6" t="s">
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="C124" s="44" t="s">
         <v>906</v>
       </c>
-      <c r="C114" s="43" t="s">
+    </row>
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="7" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="6" t="s">
+      <c r="C125" s="45" t="s">
         <v>908</v>
       </c>
-      <c r="C115" s="43" t="s">
+    </row>
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C126" s="44" t="s">
         <v>909</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="6" t="s">
-        <v>910</v>
-      </c>
-      <c r="C116" s="43" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="C117" s="43" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="C118" s="43" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="6" t="s">
-        <v>914</v>
-      </c>
-      <c r="C119" s="43" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="C120" s="43" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="C121" s="44" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="6" t="s">
-        <v>919</v>
-      </c>
-      <c r="C122" s="44" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C123" s="43" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="C124" s="43" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="C125" s="44" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C126" s="43" t="s">
-        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -9619,702 +9528,702 @@
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="46" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="24" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="24" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="24" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="24" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="24" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="24" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="24" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="24" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="24" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="24" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="23" t="s">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="24" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="23" t="s">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="24" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="7"/>
+      <c r="C18" s="24" t="s">
         <v>929</v>
       </c>
-      <c r="C5" s="23" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="24" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="23" t="s">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="24" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="23" t="s">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="24" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="23" t="s">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="24" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="23" t="s">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="24" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="23" t="s">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="24" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="23" t="s">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="24" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="24" t="s">
         <v>937</v>
       </c>
-      <c r="C12" s="45" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="24" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="23" t="s">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="24" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="23" t="s">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="24" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="24" t="s">
         <v>941</v>
       </c>
-      <c r="C15" s="23" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="24" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="23" t="s">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="5"/>
+      <c r="C32" s="24" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="23" t="s">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="24" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6"/>
-      <c r="C18" s="23" t="s">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="24" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="23" t="s">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="24" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="23" t="s">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="23" t="s">
+      <c r="C36" s="24" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="23" t="s">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="24" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="23" t="s">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="C38" s="24" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="23" t="s">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C39" s="24" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="23" t="s">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="24" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="23" t="s">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="24" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="23" t="s">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="7" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="23" t="s">
+      <c r="C42" s="24" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="23" t="s">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="24" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="23" t="s">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="23" t="s">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C45" s="24" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4"/>
-      <c r="C32" s="23" t="s">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="5" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="23" t="s">
+      <c r="C46" s="24" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="23" t="s">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C47" s="24" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="23" t="s">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C48" s="24" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4" t="s">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C49" s="24" t="s">
         <v>963</v>
       </c>
-      <c r="C36" s="23" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C50" s="24" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="23" t="s">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="7" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6" t="s">
-        <v>941</v>
-      </c>
-      <c r="C38" s="23" t="s">
+      <c r="C51" s="24" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="23" t="s">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C52" s="24" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="23" t="s">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C53" s="24" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="23" t="s">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="24" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6" t="s">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C55" s="24" t="s">
         <v>970</v>
       </c>
-      <c r="C42" s="23" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C56" s="24" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="23" t="s">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C57" s="24" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="23" t="s">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="23" t="s">
+      <c r="B58" s="7"/>
+      <c r="C58" s="24" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="s">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C59" s="24" t="s">
         <v>975</v>
       </c>
-      <c r="C46" s="23" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="24" t="s">
         <v>976</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="23" t="s">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="1" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="23" t="s">
+      <c r="C61" s="24" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="23" t="s">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C62" s="24" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="23" t="s">
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C63" s="24" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="6" t="s">
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="24" t="s">
         <v>981</v>
       </c>
-      <c r="C51" s="23" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C65" s="24" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="23" t="s">
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C66" s="24" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="23" t="s">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C67" s="24" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="23" t="s">
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C68" s="24" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="23" t="s">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C69" s="24" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="23" t="s">
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="5" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="23" t="s">
+      <c r="C70" s="24" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C71" s="24" t="s">
         <v>989</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="23" t="s">
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="24" t="s">
         <v>990</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="23" t="s">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C73" s="24" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="23" t="s">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C74" s="24" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="0" t="s">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="24" t="s">
         <v>993</v>
       </c>
-      <c r="C61" s="23" t="s">
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C76" s="24" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="23" t="s">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C77" s="24" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="23" t="s">
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="24" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="23" t="s">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="24" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="23" t="s">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="7" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="23" t="s">
+      <c r="C80" s="24" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="23" t="s">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C81" s="24" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="23" t="s">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="24" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="23" t="s">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C83" s="24" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="4" t="s">
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C84" s="24" t="s">
         <v>1004</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="23" t="s">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C85" s="24" t="s">
         <v>1005</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="23" t="s">
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C86" s="24" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C73" s="23" t="s">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="24" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="23" t="s">
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C88" s="24" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C75" s="23" t="s">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C89" s="24" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C76" s="23" t="s">
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C90" s="24" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="23" t="s">
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C91" s="24" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="23" t="s">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C92" s="24" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="23" t="s">
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C93" s="24" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="6" t="s">
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C94" s="24" t="s">
         <v>1014</v>
       </c>
-      <c r="C80" s="23" t="s">
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C95" s="24" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C81" s="23" t="s">
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C96" s="24" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="23" t="s">
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C97" s="24" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C83" s="23" t="s">
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="24" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="4" t="s">
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C99" s="24" t="s">
         <v>1019</v>
       </c>
-      <c r="C84" s="23" t="s">
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="24" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="23" t="s">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="1" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="23" t="s">
+      <c r="C101" s="24" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="23" t="s">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="7" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="23" t="s">
+      <c r="C102" s="24" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="23" t="s">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C103" s="24" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="23" t="s">
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="1" t="s">
         <v>1026</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="23" t="s">
+      <c r="C104" s="24" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C92" s="23" t="s">
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="24" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C93" s="23" t="s">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="24" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="23" t="s">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C107" s="24" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="23" t="s">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="24" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="23" t="s">
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="24" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="23" t="s">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="24" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C98" s="23" t="s">
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="24" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="23" t="s">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C112" s="1" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="23" t="s">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C113" s="1" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="0" t="s">
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C114" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="C101" s="23" t="s">
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="1" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="6" t="s">
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C116" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="C102" s="23" t="s">
+    </row>
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="1" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C103" s="23" t="s">
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="1" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="0" t="s">
+      <c r="C118" s="24" t="s">
         <v>1042</v>
       </c>
-      <c r="C104" s="23" t="s">
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="24" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="23" t="s">
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="24" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C106" s="23" t="s">
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C121" s="24" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C107" s="23" t="s">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C122" s="24" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C108" s="23" t="s">
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="24" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C109" s="23" t="s">
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C124" s="24" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C110" s="23" t="s">
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C125" s="24" t="s">
         <v>1049</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C111" s="23" t="s">
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C126" s="24" t="s">
         <v>1050</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C112" s="0" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C113" s="0" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C114" s="0" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C115" s="0" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C116" s="0" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C117" s="0" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="0" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C118" s="23" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C119" s="23" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C120" s="23" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C121" s="23" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C122" s="23" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C123" s="23" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C124" s="23" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C125" s="23" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C126" s="23" t="s">
-        <v>1066</v>
       </c>
     </row>
   </sheetData>
